--- a/borrowings_2025.xlsx
+++ b/borrowings_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sande\PycharmProjects\SLT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A917D8BA-3623-4552-99DE-B8691F3C6CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174DB8BA-B643-4AD9-BAFC-FBD900206EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5364" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{6B2E528B-688C-40AF-9ED3-50938B77F659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B2E528B-688C-40AF-9ED3-50938B77F659}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>Bank Name</t>
   </si>
@@ -60,9 +60,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -92,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -100,7 +97,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44C3779-3E7B-4816-8251-7C5CB79F4098}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -450,13 +449,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -467,10 +466,10 @@
       <c r="B2" s="2">
         <v>45672</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>1000000</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>5000</v>
       </c>
     </row>
@@ -479,13 +478,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45673</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="D3" s="3">
-        <v>5000</v>
+        <v>45677</v>
+      </c>
+      <c r="C3" s="5">
+        <v>500000</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2500</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -493,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>45674</v>
-      </c>
-      <c r="C4" s="3">
+        <v>45703</v>
+      </c>
+      <c r="C4" s="5">
         <v>1000000</v>
       </c>
-      <c r="D4" s="3">
-        <v>5000</v>
+      <c r="D4" s="5">
+        <v>5200</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,13 +506,55 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45675</v>
-      </c>
-      <c r="C5" s="3">
+        <v>45708</v>
+      </c>
+      <c r="C5" s="5">
+        <v>500000</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45731</v>
+      </c>
+      <c r="C6" s="5">
         <v>1000000</v>
       </c>
-      <c r="D5" s="3">
-        <v>5000</v>
+      <c r="D6" s="5">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45736</v>
+      </c>
+      <c r="C7" s="5">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45762</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5300</v>
       </c>
     </row>
   </sheetData>
